--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,753 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128499214</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559575</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6286784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128499273</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57679</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559501</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6286787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128499274</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57967</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559536</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6286718</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128499238</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58166</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559499</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6286801</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128499241</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57679</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559540</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6286773</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128499272</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58166</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>559494</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6286791</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128499221</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>559530</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6286667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>128499214</v>
       </c>
       <c r="B5" t="n">
-        <v>58328</v>
+        <v>58332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499273</v>
+        <v>128499274</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>57971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559501</v>
+        <v>559536</v>
       </c>
       <c r="R6" t="n">
-        <v>6286787</v>
+        <v>6286718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,32 +1237,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499274</v>
+        <v>128499273</v>
       </c>
       <c r="B7" t="n">
-        <v>57967</v>
+        <v>57683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1286,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559536</v>
+        <v>559501</v>
       </c>
       <c r="R7" t="n">
-        <v>6286718</v>
+        <v>6286787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
         <v>128499238</v>
       </c>
       <c r="B8" t="n">
-        <v>58166</v>
+        <v>58170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128499241</v>
       </c>
       <c r="B9" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128499272</v>
       </c>
       <c r="B10" t="n">
-        <v>58166</v>
+        <v>58170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128499221</v>
       </c>
       <c r="B11" t="n">
-        <v>58328</v>
+        <v>58332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1131,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499274</v>
+        <v>128499273</v>
       </c>
       <c r="B6" t="n">
-        <v>57971</v>
+        <v>57683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559536</v>
+        <v>559501</v>
       </c>
       <c r="R6" t="n">
-        <v>6286718</v>
+        <v>6286787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,6 +1211,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,32 +1242,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499273</v>
+        <v>128499274</v>
       </c>
       <c r="B7" t="n">
-        <v>57683</v>
+        <v>57971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559501</v>
+        <v>559536</v>
       </c>
       <c r="R7" t="n">
-        <v>6286787</v>
+        <v>6286718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1322,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,6 +1770,103 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128799364</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105566</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Glasporten, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>559591</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6286774</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>128499214</v>
       </c>
       <c r="B5" t="n">
-        <v>58332</v>
+        <v>58359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499273</v>
+        <v>128499274</v>
       </c>
       <c r="B6" t="n">
-        <v>57683</v>
+        <v>57998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559501</v>
+        <v>559536</v>
       </c>
       <c r="R6" t="n">
-        <v>6286787</v>
+        <v>6286718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,32 +1237,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499274</v>
+        <v>128499273</v>
       </c>
       <c r="B7" t="n">
-        <v>57971</v>
+        <v>57710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1286,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559536</v>
+        <v>559501</v>
       </c>
       <c r="R7" t="n">
-        <v>6286718</v>
+        <v>6286787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
         <v>128499238</v>
       </c>
       <c r="B8" t="n">
-        <v>58170</v>
+        <v>58197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128499241</v>
       </c>
       <c r="B9" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128499272</v>
       </c>
       <c r="B10" t="n">
-        <v>58170</v>
+        <v>58197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128499221</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1131,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499274</v>
+        <v>128499273</v>
       </c>
       <c r="B6" t="n">
-        <v>57998</v>
+        <v>57710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559536</v>
+        <v>559501</v>
       </c>
       <c r="R6" t="n">
-        <v>6286718</v>
+        <v>6286787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,6 +1211,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,32 +1242,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499273</v>
+        <v>128499274</v>
       </c>
       <c r="B7" t="n">
-        <v>57710</v>
+        <v>57998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559501</v>
+        <v>559536</v>
       </c>
       <c r="R7" t="n">
-        <v>6286787</v>
+        <v>6286718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,11 +1322,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>128499214</v>
       </c>
       <c r="B5" t="n">
-        <v>58359</v>
+        <v>58363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128499273</v>
       </c>
       <c r="B6" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>128499274</v>
       </c>
       <c r="B7" t="n">
-        <v>57998</v>
+        <v>58002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128499238</v>
       </c>
       <c r="B8" t="n">
-        <v>58197</v>
+        <v>58201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128499241</v>
       </c>
       <c r="B9" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128499272</v>
       </c>
       <c r="B10" t="n">
-        <v>58197</v>
+        <v>58201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128499221</v>
       </c>
       <c r="B11" t="n">
-        <v>58359</v>
+        <v>58363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1131,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499273</v>
+        <v>128499274</v>
       </c>
       <c r="B6" t="n">
-        <v>57714</v>
+        <v>58002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559501</v>
+        <v>559536</v>
       </c>
       <c r="R6" t="n">
-        <v>6286787</v>
+        <v>6286718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,32 +1237,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499274</v>
+        <v>128499273</v>
       </c>
       <c r="B7" t="n">
-        <v>58002</v>
+        <v>57714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1286,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559536</v>
+        <v>559501</v>
       </c>
       <c r="R7" t="n">
-        <v>6286718</v>
+        <v>6286787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1317,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>128499214</v>
       </c>
       <c r="B5" t="n">
-        <v>58363</v>
+        <v>58366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128499274</v>
       </c>
       <c r="B6" t="n">
-        <v>58002</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128499273</v>
       </c>
       <c r="B7" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>128499238</v>
       </c>
       <c r="B8" t="n">
-        <v>58201</v>
+        <v>58204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128499241</v>
       </c>
       <c r="B9" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128499272</v>
       </c>
       <c r="B10" t="n">
-        <v>58201</v>
+        <v>58204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128499221</v>
       </c>
       <c r="B11" t="n">
-        <v>58363</v>
+        <v>58366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105626</v>
+        <v>105631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105631</v>
+        <v>105634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105644</v>
+        <v>105651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105651</v>
+        <v>105653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105653</v>
+        <v>105679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -1775,7 +1775,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105679</v>
+        <v>105681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -675,50 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118036557</v>
+        <v>116250887</v>
       </c>
       <c r="B2" t="n">
-        <v>105495</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>101595</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Aspstumpbagge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platysoma deplanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Gyllenhal, 1808)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Smedstorp, Sm</t>
+          <t>Tostetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559546</v>
+        <v>559467</v>
       </c>
       <c r="R2" t="n">
-        <v>6286719</v>
+        <v>6286785</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Under bark på död asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,68 +772,73 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Per Ahlgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Per Ahlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118036558</v>
+        <v>128499241</v>
       </c>
       <c r="B3" t="n">
-        <v>5241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101423</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blankbock</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Obrium brunneum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Smedstorp, Sm</t>
+          <t>Glasporten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559563</v>
+        <v>559540</v>
       </c>
       <c r="R3" t="n">
-        <v>6286770</v>
+        <v>6286773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +885,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119743584</v>
+        <v>128499273</v>
       </c>
       <c r="B4" t="n">
-        <v>5246</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101423</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blankbock</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Obrium brunneum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -917,39 +930,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Smedstorp, Nybro, Sm</t>
+          <t>Glasporten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559586</v>
+        <v>559501</v>
       </c>
       <c r="R4" t="n">
-        <v>6286774</v>
+        <v>6286787</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,17 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På oxelblom i bryn till barrbland</t>
+          <t>vid lämpliga bo</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,63 +992,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>HLt240059</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499214</v>
+        <v>128499274</v>
       </c>
       <c r="B5" t="n">
-        <v>58366</v>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1043,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559575</v>
+        <v>559536</v>
       </c>
       <c r="R5" t="n">
-        <v>6286784</v>
+        <v>6286718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499273</v>
+        <v>128499238</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>58439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1166,7 +1149,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559501</v>
+        <v>559499</v>
       </c>
       <c r="R6" t="n">
-        <v>6286787</v>
+        <v>6286801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,17 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vid lämpliga bo</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,42 +1220,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499274</v>
+        <v>128499272</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559536</v>
+        <v>559494</v>
       </c>
       <c r="R7" t="n">
-        <v>6286718</v>
+        <v>6286791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,32 +1326,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128499238</v>
+        <v>128499214</v>
       </c>
       <c r="B8" t="n">
-        <v>58204</v>
+        <v>58602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1392,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559499</v>
+        <v>559575</v>
       </c>
       <c r="R8" t="n">
-        <v>6286801</v>
+        <v>6286784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,12 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128499241</v>
+        <v>128499221</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
+        <v>58602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1489,7 +1467,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1498,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559540</v>
+        <v>559530</v>
       </c>
       <c r="R9" t="n">
-        <v>6286773</v>
+        <v>6286667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,12 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,54 +1538,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128499272</v>
+        <v>128797681</v>
       </c>
       <c r="B10" t="n">
-        <v>58204</v>
+        <v>58790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Glasporten, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559494</v>
+        <v>559508</v>
       </c>
       <c r="R10" t="n">
-        <v>6286791</v>
+        <v>6286638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,13 +1634,14 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1666,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128499221</v>
+        <v>118036557</v>
       </c>
       <c r="B11" t="n">
-        <v>58366</v>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,43 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Glasporten, Sm</t>
+          <t>Östra Smedstorp, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559530</v>
+        <v>559546</v>
       </c>
       <c r="R11" t="n">
-        <v>6286667</v>
+        <v>6286719</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,12 +1718,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1738,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1775,7 +1753,7 @@
         <v>128799364</v>
       </c>
       <c r="B12" t="n">
-        <v>105681</v>
+        <v>106155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12506-2025 artfynd.xlsx
+++ b/artfynd/A 12506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116250887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499241</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499273</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499274</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499272</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499214</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128797681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118036557</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,8 +1899,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128799364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>